--- a/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
+++ b/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
@@ -56,14 +56,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00E8F4FA"/>
+        <bgColor rgb="00E8F4FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FA"/>
-        <bgColor rgb="00E8F4FA"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
@@ -463,13 +463,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -479,7 +479,7 @@
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="70" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,6 +583,16 @@
           <t>Pampelonne</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>info@mairie-ramatuelle.fr</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>+33 4 98 12 66 71</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -623,7 +633,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 210 boe. 60 grande plaisance + 50 résidents + 100 plagistes</t>
+          <t>Mappa Boe app — 210 boe | 60 grande plaisance + 50 résidents + 100 plagistes | Sede: Place de l'Ormeau, 83350 Ramatuelle. Police Municipale poste estivo Pampelonne parking Patch.</t>
         </is>
       </c>
     </row>
@@ -647,7 +657,7 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -676,7 +686,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 71 boe. passage jusqu'à 40m + riverains + professionnels | Lauréat Prix Thomas Joly 2024. Travaux automne 2024, ouverture mai 2025.</t>
+          <t>Mappa Boe app — 71 boe | passage jusqu'à 40m + riverains + professionnels | Lauréat Prix Thomas Joly 2024. Travaux automne 2024, ouverture mai 2025.</t>
         </is>
       </c>
     </row>
@@ -689,6 +699,16 @@
           <t>Hyères Saint-Pierre</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>contact@portshyeres.fr</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>+33 4 94 12 54 40</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -700,7 +720,7 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -729,7 +749,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 49 boe. Sud (170 ha) : 46 bouées &lt;24m + Est (75 ha) : 3 coffres 24-40m | NUOVA 2026. Installation mars-avril 2026, opérationnelle été 2026.</t>
+          <t>Mappa Boe app — 49 boe | Sud (170 ha) : 46 bouées &lt;24m + Est (75 ha) : 3 coffres 24-40m | NUOVA 2026. Installation mars-avril 2026, opérationnelle été 2026. | Sede: 116 Quai Gilles Barbanson, 83400 Hyères les Palmiers | VHF: Canal 9</t>
         </is>
       </c>
     </row>
@@ -767,7 +787,7 @@
           <t>Var, Francia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -797,7 +817,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 68 boe. 60 bouées 0-15m (4 zones) + 5 bouées 15-30m + 3 résidents &lt;15m | Usage diurne libre 8-18h, nuit payante avec réservation.</t>
+          <t>Mappa Boe app — 68 boe | 60 bouées 0-15m (4 zones) + 5 bouées 15-30m + 3 résidents &lt;15m | Usage diurne libre 8-18h, nuit payante avec réservation.</t>
         </is>
       </c>
     </row>
@@ -810,6 +830,16 @@
           <t>Agay</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>portagay@ville-saintraphael.fr</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>+33 4 94 82 74 22</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -850,7 +880,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 163 boe. 123 bouées &lt;16m + 40 places sur brise-lames &lt;5m</t>
+          <t>Mappa Boe app — 163 boe | 123 bouées &lt;16m + 40 places sur brise-lames &lt;5m | Sede: Route d'Agay RN8, 83530 AGAY | Mobile: +33 6 63 86 03 22</t>
         </is>
       </c>
     </row>
@@ -863,6 +893,11 @@
           <t>Antibes — Anse du Croûton</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>+33 4 92 90 50 00</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -874,7 +909,7 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -903,7 +938,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 47 boe. 47 bouées été (15 avr - 15 oct) / 9 bouées hiver | Site Natura 2000. Opérationnel depuis 19 juillet 2025.</t>
+          <t>Mappa Boe app — 47 boe | 47 bouées été (15 avr - 15 oct) / 9 bouées hiver | Site Natura 2000. Opérationnel depuis 19 juillet 2025. | Sede: Hôtel de Ville, Cours Masséna, 06600 Antibes</t>
         </is>
       </c>
     </row>
@@ -916,6 +951,11 @@
           <t>Villefranche-sur-Mer</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>+33 4 93 76 33 33</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -926,7 +966,7 @@
           <t>Alpes-Maritimes, Francia</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -956,7 +996,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 60 boe. 30 bouées Rochambeau + 30 bouées Palais de la Marine. 25% réservés à la plaisance de passage.</t>
+          <t>Mappa Boe app — 60 boe | 30 bouées Rochambeau + 30 bouées Palais de la Marine. 25% réservés à la plaisance de passage. | Sede: Citadelle, BP 7, 06230 Villefranche-sur-Mer</t>
         </is>
       </c>
     </row>
@@ -969,6 +1009,16 @@
           <t>Calanque de Port-Miou (Cassis)</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>portmiou@cassis.fr</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>+33 4 42 01 96 24</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -1009,7 +1059,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 487 boe. 388 bouées permanentes + 69 de passage (jour) + 30 bouées écologiques en pré-Calanque | Plus grand campo boe organisé d'France Méditerranée par capacité.</t>
+          <t>Mappa Boe app — 487 boe | 388 bouées permanentes + 69 de passage (jour) + 30 bouées écologiques en pré-Calanque | Plus grand campo boe organisé d'France Méditerranée par capacité. | Sede: 50 Avenue des Calanques, 13260 Cassis. Aperto 7/7 tutto l'anno. Port de Cassis: portdecassis@cassis.fr +33 4 42 18 35 90. | VHF: Canal 9 | Mobile: +33 6 26 84 51 58</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1093,7 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1072,7 +1122,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: in progettazione. Schéma global: 7 sites planifiés pour 2024 (Pomègues ouest/Frioul, Marseilleveyre, Sormiou, Pierres Tombées/Morgiou, Île | Interdiction d'ancrage à En-Vau et Port-Pin. Bouées obligatoires sur sites Sormiou/Morgiou. Dataset OpenData officiel disponible (geo.data.gouv.fr).</t>
+          <t>Mappa Boe app — in progettazione | Schéma global: 7 sites planifiés pour 2024 (Pomègues ouest/Frioul, Marseilleveyre, Sormiou, Pierres Tombées/Morgiou, Île | Interdiction d'ancrage à En-Vau et Port-Pin. Bouées obligatoires sur sites Sormiou/Morgiou. Dataset OpenData officiel disponible (geo.data.gouv.fr). | Sede: 141 avenue du Prado, Bâtiment A, 13008 Marseille</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1145,7 @@
           <t>Pyrénées-Orientales, Francia</t>
         </is>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -1125,7 +1175,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mappa Boe app. Capacità: 32 boe. </t>
+          <t>Mappa Boe app — 32 boe</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1199,7 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1178,7 +1228,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 52 boe. La Moulade (Collioure) 5 + Cap Gros (Port-Vendres) 16 + Sainte-Catherine (Port-Vendres) 28 + Canadells (Cerbère) 3 | 4 sites distincts. Bouées rouges (visiteurs) + bouées blanches (résidents). Mouillage gratuit, max 4h diurne sans réservation.</t>
+          <t>Mappa Boe app — 52 boe | La Moulade (Collioure) 5 + Cap Gros (Port-Vendres) 16 + Sainte-Catherine (Port-Vendres) 28 + Canadells (Cerbère) 3 | 4 sites distincts. Bouées rouges (visiteurs) + bouées blanches (résidents). Mouillage gratuit, max 4h diurne sans réservation.</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1252,7 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1231,7 +1281,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 51 boe. 51 boe — fonte Département Pyrénées-Orientales | ZMEL installée en 2023. Site Conservatoire du Littoral. Capacità verificata da PDF Confronto Sardegna-Francia (fonte: Département P-O).</t>
+          <t>Mappa Boe app — 51 boe | 51 boe — fonte Département Pyrénées-Orientales | ZMEL installée en 2023. Site Conservatoire du Littoral. Capacità verificata da PDF Confronto Sardegna-Francia (fonte: Département P-O).</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1339,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 141 boe. 33 places de passage + 108 résidents/pêcheurs/nautique | Avant la ZMEL, environ 195 mouillages sauvages. Première ZMEL Corse-du-Sud structurée à grande échelle.</t>
+          <t>Mappa Boe app — 141 boe | 33 places de passage + 108 résidents/pêcheurs/nautique | Avant la ZMEL, environ 195 mouillages sauvages. Première ZMEL Corse-du-Sud structurée à grande échelle. | Sede: 18 rue Antoine Sollacaro, 20000 Ajaccio</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1362,7 @@
           <t>Corse-du-Sud, Francia</t>
         </is>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -1342,7 +1392,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 30 boe. 3 catégories de taille: &lt;9m, 9-15m, 15-20m | Zone de mouillage organisé (ZMO), pas une ZMEL formelle. Gérée par opérateur privé.</t>
+          <t>Mappa Boe app — 30 boe | 3 catégories de taille: &lt;9m, 9-15m, 15-20m | Zone de mouillage organisé (ZMO), pas une ZMEL formelle. Gérée par opérateur privé.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1445,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: in progettazione. Mouillage régulé. Limite 2000 visiteurs/jour aux Lavezzi (QR code). ZMEL grande plaisance expérimentale max 45 navires. | 79 640 ha, 5 communes. Bouées sub-surface préconisées pour éviter le ragage.</t>
+          <t>Mappa Boe app — in progettazione | Mouillage régulé. Limite 2000 visiteurs/jour aux Lavezzi (QR code). ZMEL grande plaisance expérimentale max 45 navires. | 79 640 ha, 5 communes. Bouées sub-surface préconisées pour éviter le ragage.</t>
         </is>
       </c>
     </row>
@@ -1408,6 +1458,16 @@
           <t>Île Sainte-Marguerite — Anse Sainte-Anne (Cannes)</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>maritime@ville-cannes.fr</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>+33 4 92 18 84 84</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -1419,7 +1479,7 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1448,7 +1508,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 30 boe. 30 navires totali: 11 boe 6-8m + 8 boe 8-12m + 6 boe 12-15m + 5 boe 15-20m. Zona 5 ha + 43 ha vietato ancoraggio. Max 7  | ZMEL al nord dell'isola Sainte-Marguerite (anse Sainte-Anne). Limite ancoraggio libero, riduzione mouillage sauvage. Travaux 2019-2020.</t>
+          <t>Mappa Boe app — 30 boe | 30 navires totali: 11 boe 6-8m + 8 boe 8-12m + 6 boe 12-15m + 5 boe 15-20m. Zona 5 ha + 43 ha vietato ancoraggio. Max 7  | ZMEL al nord dell'isola Sainte-Marguerite (anse Sainte-Anne). Limite ancoraggio libero, riduzione mouillage sauvage. Travaux 2019-2020. | Sede: La Croisette, 06400 Cannes. Capitainerie Port Pierre Canto.</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1561,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 65 boe. 65 boe — gestione Nauticspot (operativo) | Campo boe operativo nella baia di Calvi gestito da Nauticspot. Distinto dal progetto istituzionale ZMEL Calvi/Revellata (50 boe in iter, vedi zmel-calvi-projet).</t>
+          <t>Mappa Boe app — 65 boe | 65 boe — gestione Nauticspot (operativo) | Campo boe operativo nella baia di Calvi gestito da Nauticspot. Distinto dal progetto istituzionale ZMEL Calvi/Revellata (50 boe in iter, vedi zmel-calvi-projet).</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1624,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Porquerolles (en projet)</t>
+          <t>Betty Buoys — progetto Porquerolles (en projet)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 354 boe. Sur 5 sites principaux de l'île | Projet majeur — 354 bouées à l'horizon 2028. Lead commercial chaud.</t>
+          <t>Mappa Boe app — 354 boe | Sur 5 sites principaux de l'île | Projet majeur — 354 bouées à l'horizon 2028. Lead commercial chaud.</t>
         </is>
       </c>
     </row>
@@ -1582,6 +1642,16 @@
           <t>Saint-Florent / San Fiurenzu (en projet)</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>mairie.saint-florent.corse@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+33 4 95 37 10 63</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Betty Buoys (sistema completo nuovo impianto)</t>
@@ -1617,12 +1687,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Saint-Florent / San Fiurenzu (en projet)</t>
+          <t>Betty Buoys — progetto Saint-Florent / San Fiurenzu (en projet)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: in progettazione. Capacité en cours d'instruction | Avis simple favorable du PNMCCA février 2025. Lead commercial chaud.</t>
+          <t>Mappa Boe app — in progettazione | Capacité en cours d'instruction | Avis simple favorable du PNMCCA février 2025. Lead commercial chaud. | Sede: 47 Rue Principale, 20217 Saint-Florent. PNMCCA contattabile via parc-marin-cap-corse-agriate.fr</t>
         </is>
       </c>
     </row>
@@ -1635,6 +1705,16 @@
           <t>Calvi + Revellata (en projet)</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>portplaisance@ville-calvi.fr</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>+33 4 95 65 10 60</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Betty Buoys (sistema completo nuovo impianto)</t>
@@ -1670,12 +1750,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Calvi + Revellata (en projet)</t>
+          <t>Betty Buoys — progetto Calvi + Revellata (en projet)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 50 boe. 2 ZMEL avec 50 bouées totales | Projet annoncé. Cible grande plaisance (jusqu'à 60m).</t>
+          <t>Mappa Boe app — 50 boe | 2 ZMEL avec 50 bouées totales | Projet annoncé. Cible grande plaisance (jusqu'à 60m). | Sede: Capitainerie du Port quai Landry, 20260 Calvi. Mairie: +33 4 95 65 82 00</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1808,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 2 boe. 2 mouillages cast iron + bouées connectées (premier en Corse) | Site pilote. Bouées connectées avec gestion à distance des réservations. Très intéressant pour Betty Buoys (proof of concept du tech).</t>
+          <t>Mappa Boe app — 2 boe | 2 mouillages cast iron + bouées connectées (premier en Corse) | Site pilote. Bouées connectées avec gestion à distance des réservations. Très intéressant pour Betty Buoys (proof of concept du tech).</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1856,12 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Zonza (5 siti)</t>
+          <t>Betty Buoys — progetto Zonza (5 siti)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 402 boe. 402 imbarcazioni ≤12m su 5 siti: Arasu (baia Saint-Cyprien), Pinarellu 1, Pinarellu 2, Ruscana, Vardiola. + 15 stelle di | MEGA progetto Corse-du-Sud Est: 402 boe su 5 siti. Inchiesta pubblica chiusa gennaio 2023. Lead commercial molto caldo per Betty Buoys.</t>
+          <t>Mappa Boe app — 402 boe | 402 imbarcazioni ≤12m su 5 siti: Arasu (baia Saint-Cyprien), Pinarellu 1, Pinarellu 2, Ruscana, Vardiola. + 15 stelle di | MEGA progetto Corse-du-Sud Est: 402 boe su 5 siti. Inchiesta pubblica chiusa gennaio 2023. Lead commercial molto caldo per Betty Buoys.</t>
         </is>
       </c>
     </row>
@@ -1829,12 +1909,12 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Plage d'Arone (Piana)</t>
+          <t>Betty Buoys — progetto Plage d'Arone (Piana)</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: in progettazione. ZMEL approvata - capacità non ancora pubblicata | Plage Arone, costa ovest Corsica. Decisione ott 2024. Sito UNESCO (Calanques di Piana). Lead commercial caldo.</t>
+          <t>Mappa Boe app — in progettazione | ZMEL approvata - capacità non ancora pubblicata | Plage Arone, costa ovest Corsica. Decisione ott 2024. Sito UNESCO (Calanques di Piana). Lead commercial caldo.</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1972,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Pointe Grenier (Saint-Cyr-sur-Mer)</t>
+          <t>Betty Buoys — progetto Pointe Grenier (Saint-Cyr-sur-Mer)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: in progettazione. Schéma global PN Calanques — 1 dei 7 siti pianificati per 2024 | Parte del schéma global del PN Calanques. Lead via PN Calanques.</t>
+          <t>Mappa Boe app — in progettazione | Schéma global PN Calanques — 1 dei 7 siti pianificati per 2024 | Parte del schéma global del PN Calanques. Lead via PN Calanques.</t>
         </is>
       </c>
     </row>
@@ -1945,12 +2025,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Betty Buoys — projet Cap Corse (Centuri/Ruglianu/Brandu — en projet)</t>
+          <t>Betty Buoys — progetto Cap Corse (Centuri/Ruglianu/Brandu — en projet)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: in progettazione. 3 communes en préparation de dossiers ZMEL | Centuri, Ruglianu et Brandu accompagnés par le PNMCCA pour leurs ZMEL. Lead commercial multi-sites.</t>
+          <t>Mappa Boe app — in progettazione | 3 communes en préparation de dossiers ZMEL | Centuri, Ruglianu et Brandu accompagnés par le PNMCCA pour leurs ZMEL. Lead commercial multi-sites.</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2093,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Campo boe in progetto. Cala Cavallo previsto 80 posti su 5.000 m² (giugno-settembre). PRRPT 2024 cita 35 posti pianifica | Cliente CRM Betty Buoys. ⚠ ATTENZIONE: campo boe non ancora installato (solo PROGETTO). Lead caldissimo per realizzazione.</t>
+          <t>Mappa Boe app — n/d | Campo boe in progetto. Cala Cavallo previsto 80 posti su 5.000 m² (giugno-settembre). PRRPT 2024 cita 35 posti pianifica | Cliente CRM Betty Buoys. ⚠ ATTENZIONE: campo boe non ancora installato (solo PROGETTO). Lead caldissimo per realizzazione. | Sede: Via Dante 1, 07026 Olbia (SS)</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2156,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 212 boe. 9 campi ormeggio storici + 30 NUOVE boe PNRR M2 C4-I3.5 (Favignana, Levanzo) installate luglio 2024. Progetto totale 17  | AMP più estesa d'Europa. Cliente CRM Betty Buoys. ESPANSIONE PNRR M2 C4-I3.5: 30 NUOVE boe installate luglio 2024 (Favignana + Levanzo). Lead caldo per espansione progetto.</t>
+          <t>Mappa Boe app — 212 boe | 9 campi ormeggio storici + 30 NUOVE boe PNRR M2 C4-I3.5 (Favignana, Levanzo) installate luglio 2024. Progetto totale 17  | AMP più estesa d'Europa. Cliente CRM Betty Buoys. ESPANSIONE PNRR M2 C4-I3.5: 30 NUOVE boe installate luglio 2024 (Favignana + Levanzo). Lead caldo per espansione progetto. | Sede: Favignana (TP)</t>
         </is>
       </c>
     </row>
@@ -2089,6 +2169,16 @@
           <t>Punta Campanella</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>info@puntacampanella.org</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>+39 081 8089877</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -2129,7 +2219,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 249 boe. Le Mortelle 35 (storico) + Isca-Crapolla 14 (2024) + 200 NUOVE boe da finanziamento PNRR €2,3M (in fase realizzazione).  | Zone B (Ieranto, Li Galli, Crapolla, Isca) ancoraggio vietato. Cliente CRM Betty Buoys. PNRR €2,3M per 200 NUOVE boe in iter realizzazione 2024-2026. Lead caldissimo per upgrade tech.</t>
+          <t>Mappa Boe app — 249 boe | Le Mortelle 35 (storico) + Isca-Crapolla 14 (2024) + 200 NUOVE boe da finanziamento PNRR €2,3M (in fase realizzazione).  | Zone B (Ieranto, Li Galli, Crapolla, Isca) ancoraggio vietato. Cliente CRM Betty Buoys. PNRR €2,3M per 200 NUOVE boe in iter realizzazione 2024-2026. Lead caldissimo per upgrade tech. | Sede: Via Roma 31, 80061 Massa Lubrense (NA). Visitor Center: lun-ven 9-13, mar/gio anche 15-18 | PEC: amppuntacampanella@pec.it | Fax: +39 081 8789663</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2277,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 100 boe. 96 boe ricreative (bianche biconiche) + 4 rosse riservate centri diving autorizzati | Velocità max 3 nodi in campo boe. Sosta ammessa fino mare forza 2.</t>
+          <t>Mappa Boe app — 100 boe | 96 boe ricreative (bianche biconiche) + 4 rosse riservate centri diving autorizzati | Velocità max 3 nodi in campo boe. Sosta ammessa fino mare forza 2. | Sede: Via Discovolo snc - c/o Stazione Manarola - 19017 Riomaggiore (SP)</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2330,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 100 boe. 100 boe — installazione Betty Buoys / Seainnova | ✓ INSTALLAZIONE BETTY BUOYS (100 boe). Costa nord Sardegna, 5.000+ ha. Monitoraggio Posidonia avviato ottobre 2024.</t>
+          <t>Mappa Boe app — 100 boe | 100 boe — installazione Betty Buoys / Seainnova | ✓ INSTALLAZIONE BETTY BUOYS (100 boe). Costa nord Sardegna, 5.000+ ha. Monitoraggio Posidonia avviato ottobre 2024. | Sede: Santa Teresa Gallura (SS)</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2353,7 @@
           <t>Sardegna, Italia</t>
         </is>
       </c>
-      <c r="I32" s="4" t="n">
+      <c r="I32" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -2293,7 +2383,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 48 boe. 48 boe totali tra Fox Mooring (Cala di Volpe) + Pevero Mooring (Golfo Pevero). Yacht 15-150m. | Operatore PRIVATO premium per superyacht in Costa Smeralda (Cala di Volpe + Pevero). Sistema ancoraggio salvaguardia fondale dall'aratura ancore yacht.</t>
+          <t>Mappa Boe app — 48 boe | 48 boe totali tra Fox Mooring (Cala di Volpe) + Pevero Mooring (Golfo Pevero). Yacht 15-150m. | Operatore PRIVATO premium per superyacht in Costa Smeralda (Cala di Volpe + Pevero). Sistema ancoraggio salvaguardia fondale dall'aratura ancore yacht. | Sede: Cala di Volpe, Costa Smeralda (SS)</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2446,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 150 boe. 89 storiche (75 campo principale + 14 Punta del Dentul Porto Conte + 4 ancoraggi intelligenti grotte) + 61 NUOVE 2025 PN | Iscrizione e autorizzazione online per boe. ESPANSIONE 2025 PNRR: 61 nuove boe installate fine giugno 2025 (Lazzaretto, Olandese, Rosso). Lead caldo per Betty Buoys.</t>
+          <t>Mappa Boe app — 150 boe | 89 storiche (75 campo principale + 14 Punta del Dentul Porto Conte + 4 ancoraggi intelligenti grotte) + 61 NUOVE 2025 PN | Iscrizione e autorizzazione online per boe. ESPANSIONE 2025 PNRR: 61 nuove boe installate fine giugno 2025 (Lazzaretto, Olandese, Rosso). Lead caldo per Betty Buoys. | Sede: Casa Gioiosa - Località Tramariglio 44, 07041 Alghero (SS) | Fax: +39 079 946507</t>
         </is>
       </c>
     </row>
@@ -2369,6 +2459,26 @@
           <t>Capo Carbonara</t>
         </is>
       </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dott. Fabrizio Atzori — Direttore</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>info@ampcapocarbonara.it</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>+39 070 790234</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -2379,8 +2489,8 @@
           <t>Sardegna, Italia</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>6</v>
+      <c r="I34" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -2389,7 +2499,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2409,7 +2519,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. 22 siti diving autorizzati, alcuni con boe sommerse</t>
+          <t>Mappa Boe app — n/d | 22 siti diving autorizzati, alcuni con boe sommerse | Sede: Via Roma 60, 09049 Villasimius (CA) | PEC: ampcapocarbonara.direzione@legalmail.it</t>
         </is>
       </c>
     </row>
@@ -2443,7 +2553,7 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2472,7 +2582,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Campi ormeggio designati attivi | Prima AMP istituita in Italia.</t>
+          <t>Mappa Boe app — n/d | Campi ormeggio designati attivi | Prima AMP istituita in Italia. | Sede: Via Petriera, 90010 Ustica (PA) | Fax: +39 091 8449194</t>
         </is>
       </c>
     </row>
@@ -2485,6 +2595,26 @@
           <t>Plemmirio</t>
         </is>
       </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Salvatore Cartarrasa — Direttore (direttore@plemmirio.it)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>info@plemmirio.it</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>+39 0931 449310</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -2525,7 +2655,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Boe a nord di Baia di Ognina (Punta Milocca - Capo Murro di Porco). Solo con autorizzazione preventiva. | Cliente CRM Betty Buoys.</t>
+          <t>Mappa Boe app — n/d | Boe a nord di Baia di Ognina (Punta Milocca - Capo Murro di Porco). Solo con autorizzazione preventiva. | Cliente CRM Betty Buoys. | Sede: Via Gaetano Abela – Comprensorio del Castello Maniace, 96100 Siracusa | PEC: consorzioplemmirio@legalletter.it | Fax: +39 0931 449954</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2688,7 @@
           <t>Puglia, Italia</t>
         </is>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -2588,7 +2718,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 69 boe. 69 boe per imbarcazioni di varie taglie</t>
+          <t>Mappa Boe app — 69 boe | 69 boe per imbarcazioni di varie taglie | Sede: Tremiti (FG)</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2752,7 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2651,7 +2781,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Gestisce sinergicamente con Torre Guaceto + CoNISMa.</t>
+          <t>Mappa Boe app — n/d | Gestisce sinergicamente con Torre Guaceto + CoNISMa. | Sede: Via Manzoni 30, 73010 Porto Cesareo (LE)</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2834,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Campo boe telematico in Zone C a 250m dalla costa | Co-gestione con Porto Cesareo + CoNISMa.</t>
+          <t>Mappa Boe app — n/d | Campo boe telematico in Zone C a 250m dalla costa | Co-gestione con Porto Cesareo + CoNISMa. | Sede: Brindisi</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2857,7 @@
           <t>Campania, Italia</t>
         </is>
       </c>
-      <c r="I40" s="4" t="n">
+      <c r="I40" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -2757,7 +2887,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 45 boe. 45 single moorings (ancoraggi a vite elicoidale) a Lacco Ameno</t>
+          <t>Mappa Boe app — 45 boe | 45 single moorings (ancoraggi a vite elicoidale) a Lacco Ameno | Sede: Ischia, Procida e Vivara</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2921,7 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2820,7 +2950,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Lampedusa, Linosa, Lampione — estremo sud Mediterraneo.</t>
+          <t>Mappa Boe app — n/d | Lampedusa, Linosa, Lampione — estremo sud Mediterraneo. | Sede: Via Cameroni, Lampedusa (AG)</t>
         </is>
       </c>
     </row>
@@ -2883,7 +3013,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Cliente CRM Betty Buoys. ATTENZIONE 2025: Ministero ha sospeso campi boe storici Tharros e Mal di Ventre. Solo Mare Morto autorizzato 2025. Sistema booking online: bluemooring.org. Lead caldissimo per</t>
+          <t>Mappa Boe app — n/d | Cliente CRM Betty Buoys. ATTENZIONE 2025: Ministero ha sospeso campi boe storici Tharros e Mal di Ventre. Solo Mare Morto autorizzato 2025. Sistema booking online: bluemooring.org. Lead caldissimo per | Sede: Corso Italia 108, 09072 Cabras (OR)</t>
         </is>
       </c>
     </row>
@@ -2896,6 +3026,26 @@
           <t>Isola dell'Asinara</t>
         </is>
       </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Vittorio Gazale — Direttore (gazale@asinara.org). Risorse marine: Aldo Zanello +39 340 181 3501 zanello@asinara.org</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>parco@asinara.org</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>+39 079 503388</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -2936,7 +3086,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: 63 boe. 63 gavitelli su 5 campi boe (versante orientale): Fornelli, Cala Reale, Punta Trabuccato, Cala del Bianco, Cala d'Oliva. | Sardegna NW, ex carcere di massima sicurezza, Parco Nazionale + AMP. Cliente CRM Betty Buoys. 5 campi: Fornelli (sud), Cala Reale, Punta Trabuccato, Cala del Bianco, Cala d'Oliva (nord). ATTENZIONE: d</t>
+          <t>Mappa Boe app — 63 boe | 63 gavitelli su 5 campi boe (versante orientale): Fornelli, Cala Reale, Punta Trabuccato, Cala del Bianco, Cala d'Oliva. | Sardegna NW, ex carcere di massima sicurezza, Parco Nazionale + AMP. Cliente CRM Betty Buoys. 5 campi: Fornelli (sud), Cala Reale, Punta Trabuccato, Cala del Bianco, Cala d'Oliva (nord). ATTENZIONE: d | Sede: Via Ponte Romano 81, 07046 Porto Torres (SS) | PEC: enteparcoasinara@pec.it | Fax: +39 079 501415</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3139,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Cale Olivetta, dell'Oro, Niasca + Cala Inglesi + 2 campi boe baia San Fruttuoso. App 'AMP Portofino' (App Store) per boo</t>
+          <t>Mappa Boe app — n/d | Cale Olivetta, dell'Oro, Niasca + Cala Inglesi + 2 campi boe baia San Fruttuoso. App 'AMP Portofino' (App Store) per boo | Sede: Portofino (GE)</t>
         </is>
       </c>
     </row>
@@ -3002,6 +3152,16 @@
           <t>Santa Maria di Castellabate</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>parco@cilentoediano.it</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>+39 0974 719911</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -3012,8 +3172,8 @@
           <t>Campania, Italia</t>
         </is>
       </c>
-      <c r="I45" t="n">
-        <v>6</v>
+      <c r="I45" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -3022,7 +3182,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3042,7 +3202,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Cilento, costa di Punta Licosa. Capacità campi ormeggio non pubblicata.</t>
+          <t>Mappa Boe app — n/d | Cilento, costa di Punta Licosa. Capacità campi ormeggio non pubblicata. | Sede: Via F. Palumbo 18, 84078 Vallo della Lucania (SA) | Fax: +39 0974 7199217</t>
         </is>
       </c>
     </row>
@@ -3055,6 +3215,16 @@
           <t>Costa degli Infreschi e della Masseta</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>parco@cilentoediano.it</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>+39 0974 719911</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -3065,8 +3235,8 @@
           <t>Campania, Italia</t>
         </is>
       </c>
-      <c r="I46" t="n">
-        <v>6</v>
+      <c r="I46" s="3" t="n">
+        <v>7</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -3075,7 +3245,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3095,7 +3265,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Zone C: ormeggio a boe per imbarcazioni eco-compatibili</t>
+          <t>Mappa Boe app — n/d | Zone C: ormeggio a boe per imbarcazioni eco-compatibili | Sede: Via F. Palumbo 18, 84078 Vallo della Lucania (SA). AMP a Marina di Camerota. | Fax: +39 0974 7199217</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3318,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d. Zona A: 5 boe gialle delimitazione + boe ormeggio in zone equipped</t>
+          <t>Mappa Boe app — n/d | Zona A: 5 boe gialle delimitazione + boe ormeggio in zone equipped | Sede: Aci Trezza (CT)</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3371,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Adriatico abruzzese.</t>
+          <t>Mappa Boe app — n/d | Adriatico abruzzese. | Sede: Pineto-Silvi (TE)</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3424,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Unica AMP del Lazio. Secche off-shore Castel Porziano.</t>
+          <t>Mappa Boe app — n/d | Unica AMP del Lazio. Secche off-shore Castel Porziano. | Sede: Roma</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3477,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mappa Boe app. Capacità: n/d. </t>
+          <t>Mappa Boe app — n/d | Sede: Bergeggi (SV)</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3530,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Prima AMP gestita da WWF. Golfo di Trieste.</t>
+          <t>Mappa Boe app — n/d | Prima AMP gestita da WWF. Golfo di Trieste. | Sede: Trieste</t>
         </is>
       </c>
     </row>
@@ -3373,6 +3543,11 @@
           <t>Capo Rizzuto</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>+39 328 8726625</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Betty Buoys (espansione PNRR)</t>
@@ -3413,7 +3588,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Ionio calabrese, area marina più estesa d'Italia per superficie. PNRR €2,5M Calabria 2024-2025 per nuovi campi ormeggio (parchi marini regionali). Lead caldo.</t>
+          <t>Mappa Boe app — n/d | Ionio calabrese, area marina più estesa d'Italia per superficie. PNRR €2,5M Calabria 2024-2025 per nuovi campi ormeggio (parchi marini regionali). Lead caldo. | Sede: Piazza Santuario, Loc. Capo Rizzuto, 88841 Isola Capo Rizzuto (KR). Provincia: Via Mario Nicoletta 28, 88900 Crotone (tel +39 0962 952111)</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3627,7 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -3481,7 +3656,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | Tirreno palermitano, costa rocciosa. Capacità campi ormeggio non pubblicata. Gestore provvisorio (in attesa istituzione gestore definitivo).</t>
+          <t>Mappa Boe app — n/d | Tirreno palermitano, costa rocciosa. Capacità campi ormeggio non pubblicata. Gestore provvisorio (in attesa istituzione gestore definitivo). | Sede: Via Francesco Crispi 153, 90133 Palermo (PA) | PEC: dm.palermo@pec.mit.gov.it</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3709,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | AMP in fase di istituzione (insieme a Bergeggi già attiva). Lead caldo per progettazione campi ormeggio.</t>
+          <t>Mappa Boe app — n/d | AMP in fase di istituzione (insieme a Bergeggi già attiva). Lead caldo per progettazione campi ormeggio. | Sede: Albenga (SV)</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3762,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Mappa Boe app. Capacità: n/d.  | AMP istituita di recente.</t>
+          <t>Mappa Boe app — n/d | AMP istituita di recente. | Sede: Milazzo (ME)</t>
         </is>
       </c>
     </row>
@@ -3610,7 +3785,7 @@
           <t>Palau, Sardegna</t>
         </is>
       </c>
-      <c r="I56" s="3" t="n">
+      <c r="I56" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -3640,7 +3815,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 32 posti. Comune Palau (NE (Gallura)) | Estremo nord Palau, Cala Inglese ("piscina di Porto Rafael"). Vista Arcipelago La Maddalena. Frequentato da vip e velisti.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 32 posti | Comune Palau (NE (Gallura)) | Estremo nord Palau, Cala Inglese ("piscina di Porto Rafael"). Vista Arcipelago La Maddalena. Frequentato da vip e velisti.</t>
         </is>
       </c>
     </row>
@@ -3653,6 +3828,21 @@
           <t>Campo Boe Campo Ormeggio Mare Azzurro Snc</t>
         </is>
       </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Tonino e Ottavio Bua (fondatori)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>mareazzurrosnc@virgilio.it</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>+39 0789 480951</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>Betty Buoys, Watch Buoy</t>
@@ -3663,7 +3853,7 @@
           <t>Olbia, Sardegna</t>
         </is>
       </c>
-      <c r="I57" s="3" t="n">
+      <c r="I57" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -3693,7 +3883,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 55 posti. Comune Olbia (NE (Gallura)) | Area Porto Istana, AMP Tavolara - Punta Coda Cavallo. Diving + noleggio + ormeggi. Fondata 1986 da Tonino e Ottavio Bua.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 55 posti | Comune Olbia (NE (Gallura)) | Area Porto Istana, AMP Tavolara - Punta Coda Cavallo. Diving + noleggio + ormeggi. Fondata 1986 da Tonino e Ottavio Bua. | Sede: Località Santa Giusta, 07026 Loiri Porto San Paolo (sede e cantiere)</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3906,7 @@
           <t>Olbia, Sardegna</t>
         </is>
       </c>
-      <c r="I58" s="3" t="n">
+      <c r="I58" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -3746,7 +3936,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 40 posti. Comune Olbia (NE (Gallura)) | Spalmatore di Terra, lato NW isola Tavolara. Coordinate da SardegnaNatura (40°53'34"N 9°40'43"E). AMP Tavolara - Punta Coda Cavallo.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 40 posti | Comune Olbia (NE (Gallura)) | Spalmatore di Terra, lato NW isola Tavolara. Coordinate da SardegnaNatura (40°53'34"N 9°40'43"E). AMP Tavolara - Punta Coda Cavallo.</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3989,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 8 posti. Comune Loiri di Porto San Paolo (NE (Gallura)) | Località Cala Finanza SNC, SS125 Orientale Sarda. Spiaggia 65m. Vicino AMP Tavolara.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 8 posti | Comune Loiri di Porto San Paolo (NE (Gallura)) | Località Cala Finanza SNC, SS125 Orientale Sarda. Spiaggia 65m. Vicino AMP Tavolara.</t>
         </is>
       </c>
     </row>
@@ -3822,7 +4012,7 @@
           <t>Loiri di Porto San Paolo, Sardegna</t>
         </is>
       </c>
-      <c r="I60" s="4" t="n">
+      <c r="I60" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -3852,7 +4042,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 27 posti. Comune Loiri di Porto San Paolo (NE (Gallura)) | Coordinate ufficiali SardegnaNatura: 40°51'30"N 9°39'15"E. AMP Tavolara - Punta Coda Cavallo.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 27 posti | Comune Loiri di Porto San Paolo (NE (Gallura)) | Coordinate ufficiali SardegnaNatura: 40°51'30"N 9°39'15"E. AMP Tavolara - Punta Coda Cavallo.</t>
         </is>
       </c>
     </row>
@@ -3905,7 +4095,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 13 posti. Comune San Teodoro (NE (Gallura)) | Coordinate verificate: 40°50'28"N 9°42'20.5"E. Anche "Spiaggia delle Farfalle". Promontorio Capo Coda Cavallo, AMP Tavolara.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 13 posti | Comune San Teodoro (NE (Gallura)) | Coordinate verificate: 40°50'28"N 9°42'20.5"E. Anche "Spiaggia delle Farfalle". Promontorio Capo Coda Cavallo, AMP Tavolara.</t>
         </is>
       </c>
     </row>
@@ -3958,7 +4148,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 10 posti. Comune San Teodoro (NE (Gallura)) | Sabbia bianca fine, area umida retrostante. Accessibile da SS125 dir. San Teodoro-Olbia, svolta dx incrocio Lutturai. AMP Tavolara.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 10 posti | Comune San Teodoro (NE (Gallura)) | Sabbia bianca fine, area umida retrostante. Accessibile da SS125 dir. San Teodoro-Olbia, svolta dx incrocio Lutturai. AMP Tavolara.</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4201,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 100 posti. Comune Dorgali (Centro-Est (Ogliastra/Nuoro)) | Campo boe più grande dei 15 censiti PRRPT 2024. Lead commerciale top per Sardegna centro-orientale. Costa Golfo di Orosei.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 100 posti | Comune Dorgali (Centro-Est (Ogliastra/Nuoro)) | Campo boe più grande dei 15 censiti PRRPT 2024. Lead commerciale top per Sardegna centro-orientale. Costa Golfo di Orosei.</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4224,7 @@
           <t>Sarroch, Sardegna</t>
         </is>
       </c>
-      <c r="I64" s="4" t="n">
+      <c r="I64" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -4064,7 +4254,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 20 posti. Comune Sarroch (SW (Sulcis)) | Costa Sarroch (Sud Cagliari). Coordinate stimate — verifica puntuale consigliata.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 20 posti | Comune Sarroch (SW (Sulcis)) | Costa Sarroch (Sud Cagliari). Coordinate stimate — verifica puntuale consigliata.</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4277,7 @@
           <t>Teulada, Sardegna</t>
         </is>
       </c>
-      <c r="I65" s="3" t="n">
+      <c r="I65" s="4" t="n">
         <v>8</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -4117,7 +4307,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 40 posti. Comune Teulada (SW (Sulcis)) | Promontorio tra Tuerredda e Piscinnì. Storico approdo fenicio-punico (VI sec a.C.). Tesoro costiero di Teulada.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 40 posti | Comune Teulada (SW (Sulcis)) | Promontorio tra Tuerredda e Piscinnì. Storico approdo fenicio-punico (VI sec a.C.). Tesoro costiero di Teulada.</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4360,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 80 posti. Comune Teulada (SW (Sulcis)) | Promontorio Capo Teulada, SW Sardegna. Spiaggia 300m. Davanti "Isola Rossa" (~1km). Lead commerciale top per Sardegna SW.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 80 posti | Comune Teulada (SW (Sulcis)) | Promontorio Capo Teulada, SW Sardegna. Spiaggia 300m. Davanti "Isola Rossa" (~1km). Lead commerciale top per Sardegna SW.</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4413,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 10 posti. Comune Portoscuso (SW (Sulcis)) | Penisola lato ovest stagno Bau Cerbus (Riserva Naturale). Sabbia bianca fine, fossili (oyster shells). Spot kitesurf.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 10 posti | Comune Portoscuso (SW (Sulcis)) | Penisola lato ovest stagno Bau Cerbus (Riserva Naturale). Sabbia bianca fine, fossili (oyster shells). Spot kitesurf.</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4436,7 @@
           <t>San Giovanni Suergiu, Sardegna</t>
         </is>
       </c>
-      <c r="I68" s="4" t="n">
+      <c r="I68" s="3" t="n">
         <v>7</v>
       </c>
       <c r="J68" t="inlineStr">
@@ -4276,7 +4466,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 20 posti. Comune San Giovanni Suergiu (SW (Sulcis)) | Villaggio costiero Sulcis, amministrazione divisa fra Portoscuso e San Giovanni Suergiu. Spiaggia 100m, sabbia beige-grigiastra. Riparata dai venti, base pescatori locali.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 20 posti | Comune San Giovanni Suergiu (SW (Sulcis)) | Villaggio costiero Sulcis, amministrazione divisa fra Portoscuso e San Giovanni Suergiu. Spiaggia 100m, sabbia beige-grigiastra. Riparata dai venti, base pescatori locali.</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4519,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Mappa Boe app. PRRPT 2024 Sardegna: 4 posti. Comune Iglesias (SW (Iglesiente)) | Frazione di Iglesias, vicino Pan di Zucchero (faraglione 133m). Sabbia dorata medio-grano, mare cristallino, fondali bassi. Sito FAI.</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 4 posti | Comune Iglesias (SW (Iglesiente)) | Frazione di Iglesias, vicino Pan di Zucchero (faraglione 133m). Sabbia dorata medio-grano, mare cristallino, fondali bassi. Sito FAI.</t>
         </is>
       </c>
     </row>

--- a/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
+++ b/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
@@ -56,14 +56,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FA"/>
-        <bgColor rgb="00E8F4FA"/>
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00E8F4FA"/>
+        <bgColor rgb="00E8F4FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -464,7 +464,7 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
@@ -479,7 +479,7 @@
     <col width="50" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="70" customWidth="1" min="18" max="18"/>
+    <col width="80" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,6 +646,21 @@
           <t>Cavalière (Le Lavandou)</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Florence MILLONI — Directrice du port (florence.milloni@le-lavandou.fr); Vincent BERENGUIER — Maître de port (vincent.berenguier@le-lavandou.fr)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>capitainerie@le-lavandou.fr</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>+33 4 94 00 41 10</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -657,7 +672,7 @@
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -686,7 +701,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 71 boe | passage jusqu'à 40m + riverains + professionnels | Lauréat Prix Thomas Joly 2024. Travaux automne 2024, ouverture mai 2025.</t>
+          <t>Mappa Boe app — 71 boe | passage jusqu'à 40m + riverains + professionnels | Lauréat Prix Thomas Joly 2024. Travaux automne 2024, ouverture mai 2025. | Sede: Quai de l'Europe - BP 100, 83980 Le Lavandou. Mairie: +33 4 94 05 15 70. Cross Med urgences: +33 4 94 61 16 16</t>
         </is>
       </c>
     </row>
@@ -719,7 +734,7 @@
           <t>Var, Francia</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -787,7 +802,7 @@
           <t>Var, Francia</t>
         </is>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -908,7 +923,7 @@
           <t>Alpes-Maritimes, Francia</t>
         </is>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -966,7 +981,7 @@
           <t>Alpes-Maritimes, Francia</t>
         </is>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -1092,7 +1107,7 @@
           <t>Bouches-du-Rhône, Francia</t>
         </is>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -1145,7 +1160,7 @@
           <t>Pyrénées-Orientales, Francia</t>
         </is>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -1199,7 +1214,7 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1252,7 +1267,7 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1362,7 +1377,7 @@
           <t>Corse-du-Sud, Francia</t>
         </is>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -1405,6 +1420,11 @@
           <t>Réserve Bouches de Bonifacio (Lavezzi)</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>+33 4 95 45 04 00</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -1415,8 +1435,8 @@
           <t>Corse-du-Sud, Francia</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>6</v>
+      <c r="I16" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1425,7 +1445,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1445,7 +1465,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Mappa Boe app — in progettazione | Mouillage régulé. Limite 2000 visiteurs/jour aux Lavezzi (QR code). ZMEL grande plaisance expérimentale max 45 navires. | 79 640 ha, 5 communes. Bouées sub-surface préconisées pour éviter le ragage.</t>
+          <t>Mappa Boe app — in progettazione | Mouillage régulé. Limite 2000 visiteurs/jour aux Lavezzi (QR code). ZMEL grande plaisance expérimentale max 45 navires. | 79 640 ha, 5 communes. Bouées sub-surface préconisées pour éviter le ragage. | Sede: Immeuble U Centru, Route de Bastia, 20137 Porto-Vecchio. Apertura: martedì e giovedì 9-12 | Mobile: +33 6 21 01 55 83</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1498,7 @@
           <t>Alpes-Maritimes, Francia</t>
         </is>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -1755,7 +1775,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 50 boe | 2 ZMEL avec 50 bouées totales | Projet annoncé. Cible grande plaisance (jusqu'à 60m). | Sede: Capitainerie du Port quai Landry, 20260 Calvi. Mairie: +33 4 95 65 82 00</t>
+          <t>Mappa Boe app — 50 boe | 2 ZMEL avec 50 bouées totales | Projet annoncé. Cible grande plaisance (jusqu'à 60m). | Sede: Capitainerie du Port quai Landry, 20260 Calvi. Mairie: +33 4 95 65 82 00 | Urgenza: +33 7 84 81 83 74</t>
         </is>
       </c>
     </row>
@@ -1821,6 +1841,11 @@
           <t>Zonza (5 siti)</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>+33 4 95 71 40 16</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Betty Buoys (sistema completo nuovo impianto)</t>
@@ -1861,7 +1886,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 402 boe | 402 imbarcazioni ≤12m su 5 siti: Arasu (baia Saint-Cyprien), Pinarellu 1, Pinarellu 2, Ruscana, Vardiola. + 15 stelle di | MEGA progetto Corse-du-Sud Est: 402 boe su 5 siti. Inchiesta pubblica chiusa gennaio 2023. Lead commercial molto caldo per Betty Buoys.</t>
+          <t>Mappa Boe app — 402 boe | 402 imbarcazioni ≤12m su 5 siti: Arasu (baia Saint-Cyprien), Pinarellu 1, Pinarellu 2, Ruscana, Vardiola. + 15 stelle di | MEGA progetto Corse-du-Sud Est: 402 boe su 5 siti. Inchiesta pubblica chiusa gennaio 2023. Lead commercial molto caldo per Betty Buoys. | Sede: Mairie de Zonza, Corse-du-Sud. Pratica ZMEL: corse-du-sud.gouv.fr (DREAL Corse)</t>
         </is>
       </c>
     </row>
@@ -1874,6 +1899,16 @@
           <t>Plage d'Arone (Piana)</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>mairie.piana@wanadoo.fr</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>+33 4 95 27 80 28</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Betty Buoys (sistema completo nuovo impianto)</t>
@@ -1914,7 +1949,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Mappa Boe app — in progettazione | ZMEL approvata - capacità non ancora pubblicata | Plage Arone, costa ovest Corsica. Decisione ott 2024. Sito UNESCO (Calanques di Piana). Lead commercial caldo.</t>
+          <t>Mappa Boe app — in progettazione | ZMEL approvata - capacità non ancora pubblicata | Plage Arone, costa ovest Corsica. Decisione ott 2024. Sito UNESCO (Calanques di Piana). Lead commercial caldo. | Sede: Place de la Mairie, 20115 Piana. Orari: lun-mar e gio-ven 09-12, 14-17; mer 09-12</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2388,7 @@
           <t>Sardegna, Italia</t>
         </is>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J32" t="inlineStr">
@@ -2489,7 +2524,7 @@
           <t>Sardegna, Italia</t>
         </is>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
@@ -2552,7 +2587,7 @@
           <t>Sicilia, Italia</t>
         </is>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J35" t="inlineStr">
@@ -2688,7 +2723,7 @@
           <t>Puglia, Italia</t>
         </is>
       </c>
-      <c r="I37" s="4" t="n">
+      <c r="I37" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J37" t="inlineStr">
@@ -2751,7 +2786,7 @@
           <t>Puglia, Italia</t>
         </is>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J38" t="inlineStr">
@@ -2857,7 +2892,7 @@
           <t>Campania, Italia</t>
         </is>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J40" t="inlineStr">
@@ -2920,7 +2955,7 @@
           <t>Sicilia, Italia</t>
         </is>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J41" t="inlineStr">
@@ -3172,7 +3207,7 @@
           <t>Campania, Italia</t>
         </is>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J45" t="inlineStr">
@@ -3235,7 +3270,7 @@
           <t>Campania, Italia</t>
         </is>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J46" t="inlineStr">
@@ -3384,6 +3419,16 @@
           <t>Secche di Tor Paterno</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>torpaterno@romanatura.roma.it</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>+39 06 35405310</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -3394,8 +3439,8 @@
           <t>Lazio, Italia</t>
         </is>
       </c>
-      <c r="I49" t="n">
-        <v>6</v>
+      <c r="I49" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -3404,7 +3449,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3424,7 +3469,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Mappa Boe app — n/d | Unica AMP del Lazio. Secche off-shore Castel Porziano. | Sede: Roma</t>
+          <t>Mappa Boe app — n/d | Unica AMP del Lazio. Secche off-shore Castel Porziano. | Sede: Villa Mazzanti, Via Gomenizza 81, 00195 Roma | PEC: romanatura@pec.regione.lazio.it | Email alt: urpromanatura@regione.lazio.it</t>
         </is>
       </c>
     </row>
@@ -3437,6 +3482,16 @@
           <t>Isola di Bergeggi</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>b.ambiente@comune.bergeggi.sv.it</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>+39 019 25790219</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -3447,8 +3502,8 @@
           <t>Liguria, Italia</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>6</v>
+      <c r="I50" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -3457,7 +3512,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3477,7 +3532,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Mappa Boe app — n/d | Sede: Bergeggi (SV)</t>
+          <t>Mappa Boe app — n/d | Sede: Via De Mari 28/D, 17028 Bergeggi (SV) | Fax: +39 019 25790220</t>
         </is>
       </c>
     </row>
@@ -3490,6 +3545,16 @@
           <t>Miramare</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>info@riservamarinamiramare.it</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>+39 040 224147</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -3500,8 +3565,8 @@
           <t>Friuli-Venezia Giulia, Italia</t>
         </is>
       </c>
-      <c r="I51" t="n">
-        <v>6</v>
+      <c r="I51" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -3510,7 +3575,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3530,7 +3595,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>Mappa Boe app — n/d | Prima AMP gestita da WWF. Golfo di Trieste. | Sede: Trieste</t>
+          <t>Mappa Boe app — n/d | Prima AMP gestita da WWF. Golfo di Trieste. | Sede: Centro Visite: Viale Miramare 349 (Parco demaniale Miramare, ex Scuderie), 34151 Trieste. Sede amministrativa: Via Beirut 7, Grignano Trieste | Email alt: info@ampmiramare.it</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3691,7 @@
           <t>Sicilia, Italia</t>
         </is>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J53" t="inlineStr">
@@ -3722,6 +3787,16 @@
           <t>Capo Milazzo</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>info@ampcapomilazzo.it</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>+39 090 9231301</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -3732,8 +3807,8 @@
           <t>Sicilia, Italia</t>
         </is>
       </c>
-      <c r="I55" t="n">
-        <v>6</v>
+      <c r="I55" s="4" t="n">
+        <v>7</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -3742,7 +3817,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>bassa</t>
+          <t>media</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3762,7 +3837,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>Mappa Boe app — n/d | AMP istituita di recente. | Sede: Milazzo (ME)</t>
+          <t>Mappa Boe app — n/d | AMP istituita di recente. | Sede: Sede legale: Via Francesco Crispi 1, 98057 Milazzo (ME). Sede operativa: P.zza Caio Duilio 21. Apertura uffici: lun-ven 9-13, mar/gio anche 15:30-17:30 | Tel alt: +39 090 922 27 90 | Mobile: +39 342 817 3143</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3860,7 @@
           <t>Palau, Sardegna</t>
         </is>
       </c>
-      <c r="I56" s="4" t="n">
+      <c r="I56" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J56" t="inlineStr">
@@ -3853,7 +3928,7 @@
           <t>Olbia, Sardegna</t>
         </is>
       </c>
-      <c r="I57" s="4" t="n">
+      <c r="I57" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J57" t="inlineStr">
@@ -3883,7 +3958,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>Mappa Boe app — PRRPT 2024 Sardegna: 55 posti | Comune Olbia (NE (Gallura)) | Area Porto Istana, AMP Tavolara - Punta Coda Cavallo. Diving + noleggio + ormeggi. Fondata 1986 da Tonino e Ottavio Bua. | Sede: Località Santa Giusta, 07026 Loiri Porto San Paolo (sede e cantiere)</t>
+          <t>Mappa Boe app — PRRPT 2024 Sardegna: 55 posti | Comune Olbia (NE (Gallura)) | Area Porto Istana, AMP Tavolara - Punta Coda Cavallo. Diving + noleggio + ormeggi. Fondata 1986 da Tonino e Ottavio Bua. | Sede: Località Santa Giusta, 07026 Loiri Porto San Paolo (sede e cantiere) | Tel Porto Istana: +39 392 1628284 | Tel Diving: +39 345 4091320</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3981,7 @@
           <t>Olbia, Sardegna</t>
         </is>
       </c>
-      <c r="I58" s="4" t="n">
+      <c r="I58" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J58" t="inlineStr">
@@ -4012,7 +4087,7 @@
           <t>Loiri di Porto San Paolo, Sardegna</t>
         </is>
       </c>
-      <c r="I60" s="3" t="n">
+      <c r="I60" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J60" t="inlineStr">
@@ -4224,7 +4299,7 @@
           <t>Sarroch, Sardegna</t>
         </is>
       </c>
-      <c r="I64" s="3" t="n">
+      <c r="I64" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J64" t="inlineStr">
@@ -4277,7 +4352,7 @@
           <t>Teulada, Sardegna</t>
         </is>
       </c>
-      <c r="I65" s="4" t="n">
+      <c r="I65" s="3" t="n">
         <v>8</v>
       </c>
       <c r="J65" t="inlineStr">
@@ -4436,7 +4511,7 @@
           <t>San Giovanni Suergiu, Sardegna</t>
         </is>
       </c>
-      <c r="I68" s="3" t="n">
+      <c r="I68" s="4" t="n">
         <v>7</v>
       </c>
       <c r="J68" t="inlineStr">

--- a/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
+++ b/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
@@ -464,8 +464,8 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
@@ -648,7 +648,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Florence MILLONI — Directrice du port (florence.milloni@le-lavandou.fr); Vincent BERENGUIER — Maître de port (vincent.berenguier@le-lavandou.fr)</t>
+          <t>Florence MILLONI</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Directrice du port (florence</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1089,7 +1094,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eloïse Faure — Chargée de mission organisation des mouillages</t>
+          <t>Eloïse Faure</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Chargée de mission organisation des mouillages</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1528,7 +1538,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 30 boe | 30 navires totali: 11 boe 6-8m + 8 boe 8-12m + 6 boe 12-15m + 5 boe 15-20m. Zona 5 ha + 43 ha vietato ancoraggio. Max 7  | ZMEL al nord dell'isola Sainte-Marguerite (anse Sainte-Anne). Limite ancoraggio libero, riduzione mouillage sauvage. Travaux 2019-2020. | Sede: La Croisette, 06400 Cannes. Capitainerie Port Pierre Canto.</t>
+          <t>Mappa Boe app — 30 boe | 30 navires totali: 11 boe 6-8m + 8 boe 8-12m + 6 boe 12-15m + 5 boe 15-20m. Zona 5 ha + 43 ha vietato ancoraggio. Max 7  | ZMEL al nord dell'isola Sainte-Marguerite (anse Sainte-Anne). Limite ancoraggio libero, riduzione mouillage sauvage. Travaux 2019-2020. | Sede: Direction Mer: La Croisette, 06400 Cannes. Port Moure Rouge (gestore operativo ZMEL): Boulevard Eugène Gazagnaire, 06400 Cannes. ONF gestisce 152 ha foreste isola. | Tel op: +33 4 93 94 37 71 | Email op: portmourerouge@ville-cannes.fr</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1974,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eloïse Faure — Chargée de mission organisation des mouillages</t>
+          <t>Eloïse Faure</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Chargée de mission organisation des mouillages</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2078,6 +2093,16 @@
           <t>Tavolara - Punta Coda Cavallo (campo boe in progetto)</t>
         </is>
       </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Augusto Navone</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>segreteria@amptavolara.it</t>
@@ -2141,6 +2166,16 @@
           <t>Isole Egadi</t>
         </is>
       </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Salvatore Livreri Console</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>info@ampisoleegadi.it</t>
@@ -2267,6 +2302,16 @@
           <t>Cinque Terre</t>
         </is>
       </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Patrizio Scarpellini</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>+39 0187 762600</t>
@@ -2325,6 +2370,16 @@
           <t>Capo Testa - Punta Falcone (Santa Teresa Gallura)</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>amp.capotesta.puntafalcone@comunestg.it</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>+39 0789 740999</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Betty Buoys, Sentinel</t>
@@ -2365,7 +2420,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 100 boe | 100 boe — installazione Betty Buoys / Seainnova | ✓ INSTALLAZIONE BETTY BUOYS (100 boe). Costa nord Sardegna, 5.000+ ha. Monitoraggio Posidonia avviato ottobre 2024. | Sede: Santa Teresa Gallura (SS)</t>
+          <t>Mappa Boe app — 100 boe | 100 boe — installazione Betty Buoys / Seainnova | ✓ INSTALLAZIONE BETTY BUOYS (100 boe). Costa nord Sardegna, 5.000+ ha. Monitoraggio Posidonia avviato ottobre 2024. | Sede: Comune di Santa Teresa Gallura, Piazza V. Emanuele I 21, 07028 Santa Teresa Gallura (SS)</t>
         </is>
       </c>
     </row>
@@ -2431,6 +2486,16 @@
           <t>Capo Caccia - Isola Piana</t>
         </is>
       </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Mariano Mariani</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>info@parcodiportoconte.it</t>
@@ -2496,7 +2561,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dott. Fabrizio Atzori — Direttore</t>
+          <t>Dott. Fabrizio Atzori</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2632,12 +2697,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salvatore Cartarrasa — Direttore (direttore@plemmirio.it)</t>
+          <t>Salvatore Cartarrasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Direttore</t>
+          <t>Direttore (direttore@plemmirio</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2703,6 +2768,16 @@
           <t>Isole Tremiti</t>
         </is>
       </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Vincenzo Totaro</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Direttore Ente Parco</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>boetremiti@prismambiente.it</t>
@@ -2710,7 +2785,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+39 348 7457462 / +39 392 0817206 (Tonino o Pasquale)</t>
+          <t>+39 348 7457462</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2753,7 +2828,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 69 boe | 69 boe per imbarcazioni di varie taglie | Sede: Tremiti (FG)</t>
+          <t>Mappa Boe app — 69 boe | 69 boe per imbarcazioni di varie taglie | Sede: Isole Tremiti (FG) | Tel alt: +39 392 0817206</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3138,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vittorio Gazale — Direttore (gazale@asinara.org). Risorse marine: Aldo Zanello +39 340 181 3501 zanello@asinara.org</t>
+          <t>Vittorio Gazale</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Direttore</t>
+          <t>Direttore (gazale@asinara</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">

--- a/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
+++ b/data/crm_seainnova_aggiornamento_mappa_boe.xlsx
@@ -466,7 +466,7 @@
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Directrice du port (florence</t>
+          <t>Directrice du port</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -784,7 +784,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Capitainerie PNF</t>
+          <t>Sophie-Dorothée DURON</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Directrice</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -837,7 +842,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 68 boe | 60 bouées 0-15m (4 zones) + 5 bouées 15-30m + 3 résidents &lt;15m | Usage diurne libre 8-18h, nuit payante avec réservation.</t>
+          <t>Mappa Boe app — 68 boe | 60 bouées 0-15m (4 zones) + 5 bouées 15-30m + 3 résidents &lt;15m | Usage diurne libre 8-18h, nuit payante avec réservation. | Sede: Île de Porquerolles, 83400 Hyères. Email dedicata progetto Porquerolles: mouillages.porquerolles@portcros-parcnational.fr | Email op: mouillages.porquerolles@portcros-parcnational.fr</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1611,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Capitainerie PNF</t>
+          <t>Sophie-Dorothée DURON</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Directrice PNF</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>capitainerie@portcros-parcnational.fr</t>
+          <t>mouillages.porquerolles@portcros-parcnational.fr</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1659,7 +1669,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 354 boe | Sur 5 sites principaux de l'île | Projet majeur — 354 bouées à l'horizon 2028. Lead commercial chaud.</t>
+          <t>Mappa Boe app — 354 boe | Sur 5 sites principaux de l'île | Projet majeur — 354 bouées à l'horizon 2028. Lead commercial chaud. | Sede: Île de Porquerolles, 83400 Hyères. Email dedicata progetto: mouillages.porquerolles@portcros-parcnational.fr | Email op: capitainerie@portcros-parcnational.fr</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1848,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Mappa Boe app — 2 boe | 2 mouillages cast iron + bouées connectées (premier en Corse) | Site pilote. Bouées connectées avec gestion à distance des réservations. Très intéressant pour Betty Buoys (proof of concept du tech).</t>
+          <t>Mappa Boe app — 2 boe | 2 mouillages cast iron + bouées connectées (premier en Corse) | Site pilote. Bouées connectées avec gestion à distance des réservations. Très intéressant pour Betty Buoys (proof of concept du tech). | Sede: Île Rousse / Bastia (Cap Corse). Riferimento istituzionale: OFB Office français de la biodiversité, ofb.gouv.fr/corse</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2090,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Mappa Boe app — in progettazione | 3 communes en préparation de dossiers ZMEL | Centuri, Ruglianu et Brandu accompagnés par le PNMCCA pour leurs ZMEL. Lead commercial multi-sites.</t>
+          <t>Mappa Boe app — in progettazione | 3 communes en préparation de dossiers ZMEL | Centuri, Ruglianu et Brandu accompagnés par le PNMCCA pour leurs ZMEL. Lead commercial multi-sites. PNRC Ajaccio +33 4 95 34 54 80 drh@pnr.corsica gestisce anche Girolata/Scandola/Porto. | Sede: Riferimento PNRC (Parc Naturel Régional de Corse): 19 avenue Georges Pompidou, Immeuble Faggianelli, CS 30417, 20184 AJACCIO CEDEX. Tel: +33 4 95 34 54 80 - Email: drh@pnr.corsica. Office Corte: La Citadelle 20250, +33 4 95 46 26 70</t>
         </is>
       </c>
     </row>
@@ -2239,6 +2249,16 @@
           <t>Punta Campanella</t>
         </is>
       </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Alberico Simeoli</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>info@puntacampanella.org</t>
@@ -2702,7 +2722,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Direttore (direttore@plemmirio</t>
+          <t>Direttore</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3073,6 +3093,16 @@
           <t>Penisola del Sinis - Mal di Ventre</t>
         </is>
       </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Massimo Marras</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Direttore</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>info.ampsinis@comune.cabras.or.it</t>
@@ -3123,7 +3153,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>Mappa Boe app — n/d | Cliente CRM Betty Buoys. ATTENZIONE 2025: Ministero ha sospeso campi boe storici Tharros e Mal di Ventre. Solo Mare Morto autorizzato 2025. Sistema booking online: bluemooring.org. Lead caldissimo per | Sede: Corso Italia 108, 09072 Cabras (OR)</t>
+          <t>Mappa Boe app — n/d | Cliente CRM Betty Buoys. ATTENZIONE 2025: Ministero ha sospeso campi boe storici Tharros e Mal di Ventre. Solo Mare Morto autorizzato 2025. Sistema booking online: bluemooring.org. Lead caldissimo per | Sede: Corso Italia 108, 09072 Cabras (OR) | Email alt: direzione.ampsinis@comune.cabras.or.it</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3173,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Direttore (gazale@asinara</t>
+          <t>Direttore</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
